--- a/pages/UATStability.xlsx
+++ b/pages/UATStability.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Motor" sheetId="1" state="visible" r:id="rId1"/>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -170,6 +170,9 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -552,8 +555,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.42578125" customWidth="1" style="2" min="1" max="1"/>
-    <col width="14" customWidth="1" style="2" min="2" max="2"/>
-    <col width="10.140625" customWidth="1" style="2" min="3" max="4"/>
+    <col width="14.42578125" customWidth="1" style="2" min="2" max="2"/>
+    <col width="11.5703125" customWidth="1" style="2" min="3" max="3"/>
+    <col width="10.140625" customWidth="1" style="2" min="4" max="4"/>
     <col width="17.42578125" customWidth="1" style="2" min="5" max="5"/>
     <col width="15" customWidth="1" style="2" min="6" max="6"/>
     <col width="21.140625" customWidth="1" style="2" min="7" max="7"/>
@@ -9991,7 +9995,7 @@
       </c>
       <c r="T118" s="6" t="n"/>
     </row>
-    <row r="119">
+    <row r="119" ht="28.5" customHeight="1">
       <c r="A119" s="3" t="n">
         <v>118</v>
       </c>
@@ -10071,7 +10075,7 @@
       </c>
       <c r="T119" s="6" t="n"/>
     </row>
-    <row r="120">
+    <row r="120" ht="28.5" customHeight="1">
       <c r="A120" s="3" t="n">
         <v>119</v>
       </c>
@@ -10151,7 +10155,7 @@
       </c>
       <c r="T120" s="6" t="n"/>
     </row>
-    <row r="121">
+    <row r="121" ht="28.5" customHeight="1">
       <c r="A121" s="3" t="n">
         <v>120</v>
       </c>
@@ -10200,7 +10204,7 @@
         <v>325.85</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M121" s="3" t="n">
         <v>325.85</v>
@@ -10231,422 +10235,1516 @@
       </c>
       <c r="T121" s="6" t="n"/>
     </row>
-    <row r="122">
-      <c r="A122" s="3" t="n"/>
-      <c r="B122" s="3" t="n"/>
-      <c r="C122" s="3" t="n"/>
-      <c r="D122" s="3" t="n"/>
-      <c r="E122" s="3" t="n"/>
-      <c r="F122" s="3" t="n"/>
-      <c r="G122" s="3" t="n"/>
-      <c r="H122" s="3" t="n"/>
-      <c r="I122" s="3" t="n"/>
-      <c r="J122" s="3" t="n"/>
-      <c r="K122" s="3" t="n"/>
-      <c r="L122" s="3" t="n"/>
-      <c r="M122" s="3" t="n"/>
-      <c r="N122" s="3" t="n"/>
-      <c r="O122" s="3" t="n"/>
-      <c r="P122" s="3" t="n"/>
-      <c r="Q122" s="3" t="n"/>
-      <c r="R122" s="4" t="n"/>
-      <c r="S122" s="4" t="n"/>
+    <row r="122" ht="30" customHeight="1">
+      <c r="A122" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>Third Party Fire &amp; Theft</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>1000073392</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>00000402000074897</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>462.28</v>
+      </c>
+      <c r="K122" s="3" t="n">
+        <v>712.5700000000001</v>
+      </c>
+      <c r="L122" s="3" t="n">
+        <v>-178.14</v>
+      </c>
+      <c r="M122" s="3" t="n">
+        <v>534.4299999999999</v>
+      </c>
+      <c r="N122" s="3" t="n">
+        <v>534.4299999999999</v>
+      </c>
+      <c r="O122" s="3" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="P122" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q122" s="3" t="n">
+        <v>587.1799999999999</v>
+      </c>
+      <c r="R122" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S122" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T122" s="6" t="n"/>
     </row>
-    <row r="123">
-      <c r="A123" s="3" t="n"/>
-      <c r="B123" s="3" t="n"/>
-      <c r="C123" s="3" t="n"/>
-      <c r="D123" s="3" t="n"/>
-      <c r="E123" s="3" t="n"/>
-      <c r="F123" s="3" t="n"/>
-      <c r="G123" s="3" t="n"/>
-      <c r="H123" s="3" t="n"/>
-      <c r="I123" s="3" t="n"/>
-      <c r="J123" s="3" t="n"/>
-      <c r="K123" s="3" t="n"/>
-      <c r="L123" s="3" t="n"/>
-      <c r="M123" s="3" t="n"/>
-      <c r="N123" s="3" t="n"/>
-      <c r="O123" s="3" t="n"/>
-      <c r="P123" s="3" t="n"/>
-      <c r="Q123" s="3" t="n"/>
-      <c r="R123" s="4" t="n"/>
-      <c r="S123" s="4" t="n"/>
+    <row r="123" ht="28.5" customHeight="1">
+      <c r="A123" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>1000073395</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>00000402000074898</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>235.53</v>
+      </c>
+      <c r="K123" s="3" t="n">
+        <v>434.47</v>
+      </c>
+      <c r="L123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="3" t="n">
+        <v>434.47</v>
+      </c>
+      <c r="N123" s="3" t="n">
+        <v>434.47</v>
+      </c>
+      <c r="O123" s="3" t="n">
+        <v>34.76</v>
+      </c>
+      <c r="P123" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q123" s="3" t="n">
+        <v>479.23</v>
+      </c>
+      <c r="R123" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S123" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T123" s="6" t="n"/>
     </row>
-    <row r="124">
-      <c r="A124" s="3" t="n"/>
-      <c r="B124" s="3" t="n"/>
-      <c r="C124" s="3" t="n"/>
-      <c r="D124" s="3" t="n"/>
-      <c r="E124" s="3" t="n"/>
-      <c r="F124" s="3" t="n"/>
-      <c r="G124" s="3" t="n"/>
-      <c r="H124" s="3" t="n"/>
-      <c r="I124" s="3" t="n"/>
-      <c r="J124" s="3" t="n"/>
-      <c r="K124" s="3" t="n"/>
-      <c r="L124" s="3" t="n"/>
-      <c r="M124" s="3" t="n"/>
-      <c r="N124" s="3" t="n"/>
-      <c r="O124" s="3" t="n"/>
-      <c r="P124" s="3" t="n"/>
-      <c r="Q124" s="3" t="n"/>
-      <c r="R124" s="4" t="n"/>
-      <c r="S124" s="4" t="n"/>
+    <row r="124" ht="28.5" customHeight="1">
+      <c r="A124" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>1000073422</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>00000402000074916</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>247.2</v>
+      </c>
+      <c r="K124" s="3" t="n">
+        <v>500.83</v>
+      </c>
+      <c r="L124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="3" t="n">
+        <v>500.83</v>
+      </c>
+      <c r="N124" s="3" t="n">
+        <v>708.83</v>
+      </c>
+      <c r="O124" s="3" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="P124" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q124" s="3" t="n">
+        <v>775.54</v>
+      </c>
+      <c r="R124" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S124" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T124" s="6" t="n"/>
     </row>
-    <row r="125">
-      <c r="A125" s="3" t="n"/>
-      <c r="B125" s="3" t="n"/>
-      <c r="C125" s="3" t="n"/>
-      <c r="D125" s="3" t="n"/>
-      <c r="E125" s="3" t="n"/>
-      <c r="F125" s="3" t="n"/>
-      <c r="G125" s="3" t="n"/>
-      <c r="H125" s="3" t="n"/>
-      <c r="I125" s="3" t="n"/>
-      <c r="J125" s="3" t="n"/>
-      <c r="K125" s="3" t="n"/>
-      <c r="L125" s="3" t="n"/>
-      <c r="M125" s="3" t="n"/>
-      <c r="N125" s="3" t="n"/>
-      <c r="O125" s="3" t="n"/>
-      <c r="P125" s="3" t="n"/>
-      <c r="Q125" s="3" t="n"/>
-      <c r="R125" s="4" t="n"/>
-      <c r="S125" s="4" t="n"/>
+    <row r="125" ht="28.5" customHeight="1">
+      <c r="A125" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>1000073893</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>00000402000075097</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>26-08-2026</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>218.32</v>
+      </c>
+      <c r="K125" s="3" t="n">
+        <v>434.47</v>
+      </c>
+      <c r="L125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="3" t="n">
+        <v>434.47</v>
+      </c>
+      <c r="N125" s="3" t="n">
+        <v>434.47</v>
+      </c>
+      <c r="O125" s="3" t="n">
+        <v>34.76</v>
+      </c>
+      <c r="P125" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q125" s="3" t="n">
+        <v>479.23</v>
+      </c>
+      <c r="R125" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S125" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T125" s="6" t="n"/>
     </row>
-    <row r="126">
-      <c r="A126" s="3" t="n"/>
-      <c r="B126" s="3" t="n"/>
-      <c r="C126" s="3" t="n"/>
-      <c r="D126" s="3" t="n"/>
-      <c r="E126" s="3" t="n"/>
-      <c r="F126" s="3" t="n"/>
-      <c r="G126" s="3" t="n"/>
-      <c r="H126" s="3" t="n"/>
-      <c r="I126" s="3" t="n"/>
-      <c r="J126" s="3" t="n"/>
-      <c r="K126" s="3" t="n"/>
-      <c r="L126" s="3" t="n"/>
-      <c r="M126" s="3" t="n"/>
-      <c r="N126" s="3" t="n"/>
-      <c r="O126" s="3" t="n"/>
-      <c r="P126" s="3" t="n"/>
-      <c r="Q126" s="3" t="n"/>
-      <c r="R126" s="4" t="n"/>
-      <c r="S126" s="4" t="n"/>
+    <row r="126" ht="28.5" customHeight="1">
+      <c r="A126" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>1000074056</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>27-08-2026</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>491.67</v>
+      </c>
+      <c r="K126" s="3" t="n">
+        <v>1096.26</v>
+      </c>
+      <c r="L126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="3" t="n">
+        <v>1096.26</v>
+      </c>
+      <c r="N126" s="3" t="n">
+        <v>1377.24</v>
+      </c>
+      <c r="O126" s="3" t="n">
+        <v>110.18</v>
+      </c>
+      <c r="P126" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q126" s="3" t="n">
+        <v>1497.42</v>
+      </c>
+      <c r="R126" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S126" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T126" s="6" t="n"/>
     </row>
-    <row r="127">
-      <c r="A127" s="3" t="n"/>
-      <c r="B127" s="3" t="n"/>
-      <c r="C127" s="3" t="n"/>
-      <c r="D127" s="3" t="n"/>
-      <c r="E127" s="3" t="n"/>
-      <c r="F127" s="3" t="n"/>
-      <c r="G127" s="3" t="n"/>
-      <c r="H127" s="3" t="n"/>
-      <c r="I127" s="3" t="n"/>
-      <c r="J127" s="3" t="n"/>
-      <c r="K127" s="3" t="n"/>
-      <c r="L127" s="3" t="n"/>
-      <c r="M127" s="3" t="n"/>
-      <c r="N127" s="3" t="n"/>
-      <c r="O127" s="3" t="n"/>
-      <c r="P127" s="3" t="n"/>
-      <c r="Q127" s="3" t="n"/>
-      <c r="R127" s="4" t="n"/>
-      <c r="S127" s="4" t="n"/>
+    <row r="127" ht="28.5" customHeight="1">
+      <c r="A127" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>1000074066</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>00000402000075155</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>27-08-2026</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="J127" s="3" t="n">
+        <v>256.79</v>
+      </c>
+      <c r="K127" s="3" t="n">
+        <v>646.1</v>
+      </c>
+      <c r="L127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="3" t="n">
+        <v>646.1</v>
+      </c>
+      <c r="N127" s="3" t="n">
+        <v>646.1</v>
+      </c>
+      <c r="O127" s="3" t="n">
+        <v>51.69</v>
+      </c>
+      <c r="P127" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q127" s="3" t="n">
+        <v>707.79</v>
+      </c>
+      <c r="R127" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S127" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T127" s="6" t="n"/>
     </row>
-    <row r="128">
-      <c r="A128" s="3" t="n"/>
-      <c r="B128" s="3" t="n"/>
-      <c r="C128" s="3" t="n"/>
-      <c r="D128" s="3" t="n"/>
-      <c r="E128" s="3" t="n"/>
-      <c r="F128" s="3" t="n"/>
-      <c r="G128" s="3" t="n"/>
-      <c r="H128" s="3" t="n"/>
-      <c r="I128" s="3" t="n"/>
-      <c r="J128" s="3" t="n"/>
-      <c r="K128" s="3" t="n"/>
-      <c r="L128" s="3" t="n"/>
-      <c r="M128" s="3" t="n"/>
-      <c r="N128" s="3" t="n"/>
-      <c r="O128" s="3" t="n"/>
-      <c r="P128" s="3" t="n"/>
-      <c r="Q128" s="3" t="n"/>
-      <c r="R128" s="4" t="n"/>
-      <c r="S128" s="4" t="n"/>
+    <row r="128" ht="30" customHeight="1">
+      <c r="A128" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>Third Party Fire &amp; Theft</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>1000074327</t>
+        </is>
+      </c>
+      <c r="G128" s="15" t="n">
+        <v>402000075262</v>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>01-09-2026</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>398.04</v>
+      </c>
+      <c r="L128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="3" t="n">
+        <v>398.04</v>
+      </c>
+      <c r="N128" s="3" t="n">
+        <v>398.04</v>
+      </c>
+      <c r="O128" s="3" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="P128" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q128" s="3" t="n">
+        <v>439.88</v>
+      </c>
+      <c r="R128" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S128" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T128" s="6" t="n"/>
     </row>
-    <row r="129">
-      <c r="A129" s="3" t="n"/>
-      <c r="B129" s="3" t="n"/>
-      <c r="C129" s="3" t="n"/>
-      <c r="D129" s="3" t="n"/>
-      <c r="E129" s="3" t="n"/>
-      <c r="F129" s="3" t="n"/>
-      <c r="G129" s="3" t="n"/>
-      <c r="H129" s="3" t="n"/>
-      <c r="I129" s="3" t="n"/>
-      <c r="J129" s="3" t="n"/>
-      <c r="K129" s="3" t="n"/>
-      <c r="L129" s="3" t="n"/>
-      <c r="M129" s="3" t="n"/>
-      <c r="N129" s="3" t="n"/>
-      <c r="O129" s="3" t="n"/>
-      <c r="P129" s="3" t="n"/>
-      <c r="Q129" s="3" t="n"/>
-      <c r="R129" s="4" t="n"/>
-      <c r="S129" s="4" t="n"/>
+    <row r="129" ht="28.5" customHeight="1">
+      <c r="A129" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>MC</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>1000074624</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>00000402000075436</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>94.06</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="N129" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="O129" s="3" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="P129" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q129" s="3" t="n">
+        <v>178.48</v>
+      </c>
+      <c r="R129" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S129" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T129" s="6" t="n"/>
     </row>
-    <row r="130">
-      <c r="A130" s="3" t="n"/>
-      <c r="B130" s="3" t="n"/>
-      <c r="C130" s="3" t="n"/>
-      <c r="D130" s="3" t="n"/>
-      <c r="E130" s="3" t="n"/>
-      <c r="F130" s="3" t="n"/>
-      <c r="G130" s="3" t="n"/>
-      <c r="H130" s="3" t="n"/>
-      <c r="I130" s="3" t="n"/>
-      <c r="J130" s="3" t="n"/>
-      <c r="K130" s="3" t="n"/>
-      <c r="L130" s="3" t="n"/>
-      <c r="M130" s="3" t="n"/>
-      <c r="N130" s="3" t="n"/>
-      <c r="O130" s="3" t="n"/>
-      <c r="P130" s="3" t="n"/>
-      <c r="Q130" s="3" t="n"/>
-      <c r="R130" s="4" t="n"/>
-      <c r="S130" s="4" t="n"/>
+    <row r="130" ht="28.5" customHeight="1">
+      <c r="A130" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>MC</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>1000074644</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>00000402000075444</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>8100</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>187.48</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>310.92</v>
+      </c>
+      <c r="L130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="3" t="n">
+        <v>310.92</v>
+      </c>
+      <c r="N130" s="3" t="n">
+        <v>310.92</v>
+      </c>
+      <c r="O130" s="3" t="n">
+        <v>24.87</v>
+      </c>
+      <c r="P130" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q130" s="3" t="n">
+        <v>345.79</v>
+      </c>
+      <c r="R130" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S130" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T130" s="6" t="n"/>
     </row>
-    <row r="131">
-      <c r="A131" s="3" t="n"/>
-      <c r="B131" s="3" t="n"/>
-      <c r="C131" s="3" t="n"/>
-      <c r="D131" s="3" t="n"/>
-      <c r="E131" s="3" t="n"/>
-      <c r="F131" s="3" t="n"/>
-      <c r="G131" s="3" t="n"/>
-      <c r="H131" s="3" t="n"/>
-      <c r="I131" s="3" t="n"/>
-      <c r="J131" s="3" t="n"/>
-      <c r="K131" s="3" t="n"/>
-      <c r="L131" s="3" t="n"/>
-      <c r="M131" s="3" t="n"/>
-      <c r="N131" s="3" t="n"/>
-      <c r="O131" s="3" t="n"/>
-      <c r="P131" s="3" t="n"/>
-      <c r="Q131" s="3" t="n"/>
-      <c r="R131" s="4" t="n"/>
-      <c r="S131" s="4" t="n"/>
+    <row r="131" ht="28.5" customHeight="1">
+      <c r="A131" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>MC</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>1000074646</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>00000402000075445</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>94.06</v>
+      </c>
+      <c r="K131" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="L131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="N131" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="O131" s="3" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="P131" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q131" s="3" t="n">
+        <v>178.48</v>
+      </c>
+      <c r="R131" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S131" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T131" s="6" t="n"/>
     </row>
-    <row r="132">
-      <c r="A132" s="3" t="n"/>
-      <c r="B132" s="3" t="n"/>
-      <c r="C132" s="3" t="n"/>
-      <c r="D132" s="3" t="n"/>
-      <c r="E132" s="3" t="n"/>
-      <c r="F132" s="3" t="n"/>
-      <c r="G132" s="3" t="n"/>
-      <c r="H132" s="3" t="n"/>
-      <c r="I132" s="3" t="n"/>
-      <c r="J132" s="3" t="n"/>
-      <c r="K132" s="3" t="n"/>
-      <c r="L132" s="3" t="n"/>
-      <c r="M132" s="3" t="n"/>
-      <c r="N132" s="3" t="n"/>
-      <c r="O132" s="3" t="n"/>
-      <c r="P132" s="3" t="n"/>
-      <c r="Q132" s="3" t="n"/>
-      <c r="R132" s="4" t="n"/>
-      <c r="S132" s="4" t="n"/>
+    <row r="132" ht="28.5" customHeight="1">
+      <c r="A132" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>1000074750</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>00000402000075473</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>07-09-2026</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v>24300</v>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>393.46</v>
+      </c>
+      <c r="K132" s="3" t="n">
+        <v>1273.7</v>
+      </c>
+      <c r="L132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="3" t="n">
+        <v>1273.7</v>
+      </c>
+      <c r="N132" s="3" t="n">
+        <v>1273.7</v>
+      </c>
+      <c r="O132" s="3" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="P132" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q132" s="3" t="n">
+        <v>1385.6</v>
+      </c>
+      <c r="R132" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S132" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T132" s="6" t="n"/>
     </row>
-    <row r="133">
-      <c r="A133" s="3" t="n"/>
-      <c r="B133" s="3" t="n"/>
-      <c r="C133" s="3" t="n"/>
-      <c r="D133" s="3" t="n"/>
-      <c r="E133" s="3" t="n"/>
-      <c r="F133" s="3" t="n"/>
-      <c r="G133" s="3" t="n"/>
-      <c r="H133" s="3" t="n"/>
-      <c r="I133" s="3" t="n"/>
-      <c r="J133" s="3" t="n"/>
-      <c r="K133" s="3" t="n"/>
-      <c r="L133" s="3" t="n"/>
-      <c r="M133" s="3" t="n"/>
-      <c r="N133" s="3" t="n"/>
-      <c r="O133" s="3" t="n"/>
-      <c r="P133" s="3" t="n"/>
-      <c r="Q133" s="3" t="n"/>
-      <c r="R133" s="4" t="n"/>
-      <c r="S133" s="4" t="n"/>
+    <row r="133" ht="30" customHeight="1">
+      <c r="A133" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>Third Party Fire &amp; Theft</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>1000074815</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>00000402000075515</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2026</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>3400</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>281.62</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>330.77</v>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="3" t="n">
+        <v>330.77</v>
+      </c>
+      <c r="N133" s="3" t="n">
+        <v>330.77</v>
+      </c>
+      <c r="O133" s="3" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="P133" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q133" s="3" t="n">
+        <v>367.23</v>
+      </c>
+      <c r="R133" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S133" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T133" s="6" t="n"/>
     </row>
-    <row r="134">
-      <c r="A134" s="3" t="n"/>
-      <c r="B134" s="3" t="n"/>
-      <c r="C134" s="3" t="n"/>
-      <c r="D134" s="3" t="n"/>
-      <c r="E134" s="3" t="n"/>
-      <c r="F134" s="3" t="n"/>
-      <c r="G134" s="3" t="n"/>
-      <c r="H134" s="3" t="n"/>
-      <c r="I134" s="3" t="n"/>
-      <c r="J134" s="3" t="n"/>
-      <c r="K134" s="3" t="n"/>
-      <c r="L134" s="3" t="n"/>
-      <c r="M134" s="3" t="n"/>
-      <c r="N134" s="3" t="n"/>
-      <c r="O134" s="3" t="n"/>
-      <c r="P134" s="3" t="n"/>
-      <c r="Q134" s="3" t="n"/>
-      <c r="R134" s="4" t="n"/>
-      <c r="S134" s="4" t="n"/>
+    <row r="134" ht="28.5" customHeight="1">
+      <c r="A134" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F134" s="14" t="n">
+        <v>1000074823</v>
+      </c>
+      <c r="G134" s="15" t="n">
+        <v>402000075518</v>
+      </c>
+      <c r="H134" s="16" t="n">
+        <v>46274</v>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J134" s="3" t="n">
+        <v>491.67</v>
+      </c>
+      <c r="K134" s="3" t="n">
+        <v>330.77</v>
+      </c>
+      <c r="L134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="3" t="n">
+        <v>330.77</v>
+      </c>
+      <c r="N134" s="3" t="n">
+        <v>330.77</v>
+      </c>
+      <c r="O134" s="3" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="P134" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q134" s="3" t="n">
+        <v>367.23</v>
+      </c>
+      <c r="R134" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S134" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T134" s="6" t="n"/>
     </row>
-    <row r="135">
-      <c r="A135" s="3" t="n"/>
-      <c r="B135" s="3" t="n"/>
-      <c r="C135" s="3" t="n"/>
-      <c r="D135" s="3" t="n"/>
-      <c r="E135" s="3" t="n"/>
-      <c r="F135" s="3" t="n"/>
-      <c r="G135" s="3" t="n"/>
-      <c r="H135" s="3" t="n"/>
-      <c r="I135" s="3" t="n"/>
-      <c r="J135" s="3" t="n"/>
-      <c r="K135" s="3" t="n"/>
-      <c r="L135" s="3" t="n"/>
-      <c r="M135" s="3" t="n"/>
-      <c r="N135" s="3" t="n"/>
-      <c r="O135" s="3" t="n"/>
-      <c r="P135" s="3" t="n"/>
-      <c r="Q135" s="3" t="n"/>
-      <c r="R135" s="4" t="n"/>
-      <c r="S135" s="4" t="n"/>
+    <row r="135" ht="28.5" customHeight="1">
+      <c r="A135" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>1000074839</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>00000402000075522</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2026</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>491.67</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>1096.26</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>1096.26</v>
+      </c>
+      <c r="N135" s="3" t="n">
+        <v>1377.24</v>
+      </c>
+      <c r="O135" s="3" t="n">
+        <v>110.18</v>
+      </c>
+      <c r="P135" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q135" s="3" t="n">
+        <v>1497.42</v>
+      </c>
+      <c r="R135" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S135" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T135" s="6" t="n"/>
     </row>
-    <row r="136">
-      <c r="A136" s="3" t="n"/>
-      <c r="B136" s="3" t="n"/>
-      <c r="C136" s="3" t="n"/>
-      <c r="D136" s="3" t="n"/>
-      <c r="E136" s="3" t="n"/>
-      <c r="F136" s="3" t="n"/>
-      <c r="G136" s="3" t="n"/>
-      <c r="H136" s="3" t="n"/>
-      <c r="I136" s="3" t="n"/>
-      <c r="J136" s="3" t="n"/>
-      <c r="K136" s="3" t="n"/>
-      <c r="L136" s="3" t="n"/>
-      <c r="M136" s="3" t="n"/>
-      <c r="N136" s="3" t="n"/>
-      <c r="O136" s="3" t="n"/>
-      <c r="P136" s="3" t="n"/>
-      <c r="Q136" s="3" t="n"/>
-      <c r="R136" s="4" t="n"/>
-      <c r="S136" s="4" t="n"/>
+    <row r="136" ht="30" customHeight="1">
+      <c r="A136" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>Third Party Fire &amp; Theft</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>1000075049</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>00000402000075582</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>10-09-2026</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J136" s="3" t="n">
+        <v>278.13</v>
+      </c>
+      <c r="K136" s="3" t="n">
+        <v>325.85</v>
+      </c>
+      <c r="L136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="3" t="n">
+        <v>325.85</v>
+      </c>
+      <c r="N136" s="3" t="n">
+        <v>325.85</v>
+      </c>
+      <c r="O136" s="3" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="P136" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q136" s="3" t="n">
+        <v>361.92</v>
+      </c>
+      <c r="R136" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S136" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T136" s="6" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n"/>
-      <c r="B137" s="3" t="n"/>
-      <c r="C137" s="3" t="n"/>
-      <c r="D137" s="3" t="n"/>
-      <c r="E137" s="3" t="n"/>
-      <c r="F137" s="3" t="n"/>
-      <c r="G137" s="3" t="n"/>
-      <c r="H137" s="3" t="n"/>
-      <c r="I137" s="3" t="n"/>
-      <c r="J137" s="3" t="n"/>
-      <c r="K137" s="3" t="n"/>
-      <c r="L137" s="3" t="n"/>
-      <c r="M137" s="3" t="n"/>
-      <c r="N137" s="3" t="n"/>
-      <c r="O137" s="3" t="n"/>
-      <c r="P137" s="3" t="n"/>
-      <c r="Q137" s="3" t="n"/>
-      <c r="R137" s="4" t="n"/>
-      <c r="S137" s="4" t="n"/>
+      <c r="A137" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>1000075072</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>00000402000075590</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>10-09-2026</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="n">
+        <v>23700</v>
+      </c>
+      <c r="J137" s="3" t="n">
+        <v>386.13</v>
+      </c>
+      <c r="K137" s="3" t="n">
+        <v>1239.31</v>
+      </c>
+      <c r="L137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="3" t="n">
+        <v>1239.31</v>
+      </c>
+      <c r="N137" s="3" t="n">
+        <v>1239.31</v>
+      </c>
+      <c r="O137" s="3" t="n">
+        <v>99.15000000000001</v>
+      </c>
+      <c r="P137" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q137" s="3" t="n">
+        <v>1348.46</v>
+      </c>
+      <c r="R137" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S137" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T137" s="6" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n"/>
-      <c r="B138" s="3" t="n"/>
-      <c r="C138" s="3" t="n"/>
-      <c r="D138" s="3" t="n"/>
-      <c r="E138" s="3" t="n"/>
-      <c r="F138" s="3" t="n"/>
-      <c r="G138" s="3" t="n"/>
-      <c r="H138" s="3" t="n"/>
-      <c r="I138" s="3" t="n"/>
-      <c r="J138" s="3" t="n"/>
-      <c r="K138" s="3" t="n"/>
-      <c r="L138" s="3" t="n"/>
-      <c r="M138" s="3" t="n"/>
-      <c r="N138" s="3" t="n"/>
-      <c r="O138" s="3" t="n"/>
-      <c r="P138" s="3" t="n"/>
-      <c r="Q138" s="3" t="n"/>
-      <c r="R138" s="4" t="n"/>
-      <c r="S138" s="4" t="n"/>
+      <c r="A138" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>1000075077</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>00000402000075594</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>10-09-2026</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J138" s="3" t="n">
+        <v>296.31</v>
+      </c>
+      <c r="K138" s="3" t="n">
+        <v>573.3</v>
+      </c>
+      <c r="L138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="3" t="n">
+        <v>573.3</v>
+      </c>
+      <c r="N138" s="3" t="n">
+        <v>573.3</v>
+      </c>
+      <c r="O138" s="3" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="P138" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q138" s="3" t="n">
+        <v>629.16</v>
+      </c>
+      <c r="R138" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S138" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T138" s="6" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n"/>
-      <c r="B139" s="3" t="n"/>
-      <c r="C139" s="3" t="n"/>
-      <c r="D139" s="3" t="n"/>
-      <c r="E139" s="3" t="n"/>
-      <c r="F139" s="3" t="n"/>
-      <c r="G139" s="3" t="n"/>
-      <c r="H139" s="3" t="n"/>
-      <c r="I139" s="3" t="n"/>
-      <c r="J139" s="3" t="n"/>
-      <c r="K139" s="3" t="n"/>
-      <c r="L139" s="3" t="n"/>
-      <c r="M139" s="3" t="n"/>
-      <c r="N139" s="3" t="n"/>
-      <c r="O139" s="3" t="n"/>
-      <c r="P139" s="3" t="n"/>
-      <c r="Q139" s="3" t="n"/>
-      <c r="R139" s="4" t="n"/>
-      <c r="S139" s="4" t="n"/>
+      <c r="A139" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>1000075108</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>00000402000075720</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>19400</v>
+      </c>
+      <c r="J139" s="3" t="n">
+        <v>359.81</v>
+      </c>
+      <c r="K139" s="3" t="n">
+        <v>1101.77</v>
+      </c>
+      <c r="L139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="3" t="n">
+        <v>1101.77</v>
+      </c>
+      <c r="N139" s="3" t="n">
+        <v>1101.77</v>
+      </c>
+      <c r="O139" s="3" t="n">
+        <v>88.14</v>
+      </c>
+      <c r="P139" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q139" s="3" t="n">
+        <v>1199.91</v>
+      </c>
+      <c r="R139" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S139" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T139" s="6" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n"/>
-      <c r="B140" s="3" t="n"/>
-      <c r="C140" s="3" t="n"/>
-      <c r="D140" s="3" t="n"/>
-      <c r="E140" s="3" t="n"/>
-      <c r="F140" s="3" t="n"/>
-      <c r="G140" s="3" t="n"/>
-      <c r="H140" s="3" t="n"/>
-      <c r="I140" s="3" t="n"/>
-      <c r="J140" s="3" t="n"/>
-      <c r="K140" s="3" t="n"/>
-      <c r="L140" s="3" t="n"/>
-      <c r="M140" s="3" t="n"/>
-      <c r="N140" s="3" t="n"/>
-      <c r="O140" s="3" t="n"/>
-      <c r="P140" s="3" t="n"/>
-      <c r="Q140" s="3" t="n"/>
-      <c r="R140" s="4" t="n"/>
-      <c r="S140" s="4" t="n"/>
+      <c r="A140" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>MC</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>Comprehensive</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>1000075112</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>00000402000075722</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="n">
+        <v>11300</v>
+      </c>
+      <c r="J140" s="3" t="n">
+        <v>192.83</v>
+      </c>
+      <c r="K140" s="3" t="n">
+        <v>376.2</v>
+      </c>
+      <c r="L140" s="3" t="n">
+        <v>-56.43</v>
+      </c>
+      <c r="M140" s="3" t="n">
+        <v>319.77</v>
+      </c>
+      <c r="N140" s="3" t="n">
+        <v>319.77</v>
+      </c>
+      <c r="O140" s="3" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="P140" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q140" s="3" t="n">
+        <v>355.35</v>
+      </c>
+      <c r="R140" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="S140" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="T140" s="6" t="n"/>
     </row>
     <row r="141">
@@ -16014,7 +17112,7 @@
   <cols>
     <col width="7.28515625" customWidth="1" min="1" max="1"/>
     <col width="14.42578125" customWidth="1" min="2" max="2"/>
-    <col width="10.5703125" customWidth="1" min="3" max="3"/>
+    <col width="11.7109375" customWidth="1" min="3" max="3"/>
     <col width="14.7109375" customWidth="1" style="2" min="5" max="5"/>
     <col width="13.7109375" customWidth="1" style="2" min="6" max="6"/>
     <col width="13.85546875" customWidth="1" min="7" max="7"/>
@@ -18057,44 +19155,156 @@
       </c>
       <c r="R27" s="6" t="n"/>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="6" t="n"/>
-      <c r="L28" s="6" t="n"/>
-      <c r="M28" s="6" t="n"/>
-      <c r="N28" s="6" t="n"/>
-      <c r="O28" s="6" t="n"/>
-      <c r="P28" s="4" t="n"/>
-      <c r="Q28" s="4" t="n"/>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Personal Accident Safe</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Full-Time Student</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>1000074336</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>00000402000075264</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>01-09-2026</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>262</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O28" s="6" t="n">
+        <v>222.22</v>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="R28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
-      <c r="M29" s="6" t="n"/>
-      <c r="N29" s="6" t="n"/>
-      <c r="O29" s="6" t="n"/>
-      <c r="P29" s="4" t="n"/>
-      <c r="Q29" s="4" t="n"/>
+      <c r="A29" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Personal Accident Safe</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Full-Time Student</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>1000075078</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>00000402000075595</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>10-09-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>262</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>239.2</v>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>Downloaded Automatically
+Validated Manually</t>
+        </is>
+      </c>
       <c r="R29" s="6" t="n"/>
     </row>
     <row r="30">
